--- a/report/workbooks/cg_workbook_values.xlsx
+++ b/report/workbooks/cg_workbook_values.xlsx
@@ -17,19 +17,25 @@
     <sheet name="Color_Interp" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Ray_Tracing" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="Thermal_Kernels" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Duty_Cycle" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="Performance" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Tracking" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Line_Follower" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Explosion" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Duty_Cycle" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Performance" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Clipping!$A$1:$U$42</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Color_Interp!$A$1:$U$36</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Decomposition!$A$1:$T$202</definedName>
-    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">Duty_Cycle!$A$1:$Z$34</definedName>
+    <definedName function="false" hidden="false" localSheetId="12" name="_xlnm.Print_Area" vbProcedure="false">Duty_Cycle!$A$1:$Z$34</definedName>
+    <definedName function="false" hidden="false" localSheetId="11" name="_xlnm.Print_Area" vbProcedure="false">Explosion!$A$1:$S$56</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Illumination!$A$1:$K$54</definedName>
-    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">Performance!$A$1:$I$39</definedName>
+    <definedName function="false" hidden="false" localSheetId="10" name="_xlnm.Print_Area" vbProcedure="false">Line_Follower!$A$1:$M$26</definedName>
+    <definedName function="false" hidden="false" localSheetId="13" name="_xlnm.Print_Area" vbProcedure="false">Performance!$A$1:$I$39</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Primitives!$A$1:$Q$31</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Ray_Tracing!$A$1:$J$39</definedName>
     <definedName function="false" hidden="false" localSheetId="8" name="_xlnm.Print_Area" vbProcedure="false">Thermal_Kernels!$A$1:$Z$28</definedName>
+    <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">Tracking!$A$1:$U$42</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Transform_Trace!$A$1:$T$44</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">View_Projection!$A$1:$M$40</definedName>
   </definedNames>
@@ -43,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="1032">
   <si>
     <t xml:space="preserve">Primitives: vertex and triangle counts of the real mesh generators</t>
   </si>
@@ -2575,6 +2581,363 @@
   </si>
   <si>
     <t xml:space="preserve">The Frame Explorer shows Gx, Gy with bias 0.5 (zero = mid-grey); Sobel |G| uses both kernels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tracking: Kalman predict / gate / update, two-view triangulation, time on target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: vision/MultiTracker.cpp predict, mahalanobis2, kalmanUpdate, triangulate; ai/Squad.cpp roundFlightTime, planStrike. Worked example values in yellow; q, gate, flight model from --export-docs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Predict: x' = F x, P' = F P F^T + Q (white-noise acceleration q)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dt (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">q (m/s2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meas. sigma (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x = (x, z, vx, vz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P (before)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x' = F x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P' = F P F^T + Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Gate and update with a measurement m (ground point)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. Time on target (roundFlightTime, planStrike)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m = (x, z)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">accel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ramp (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cruise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fuse (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation nu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S = H P' H^T + sigma^2 I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S^-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K = P' H^T S^-1 (4x2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x_new = x' + K nu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">distance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d - fuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ramp dist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">launch +s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">both rounds arrive together: launch delay = T_far - T_k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d^2 = nu^T S^-1 nu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. Two-view triangulation: minimise |o1 + s d1 - (o2 + t d2)|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o1 (UAV 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o2 (UAV 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a = d1.d1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b = d1.d2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c = d2.d2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d = d1.w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e = d2.w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p1 = o1 + s d1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p2 = o2 + t d2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">midpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">residual |p1-p2|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line_Follower: IR sensor array, PD steering, differential drive (one tick)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: ai/HideController.cpp followLine (kSensorForward, kSensorSpacing, kLineHalfWidth, kKp, kKd, kMaxSpeed); objects/Rover.h kRoverTrackWidth. Line offset, previous error and dt are worked-example inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spacing (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">half width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">err scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slow-down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">omega max</t>
+  </si>
+  <si>
+    <t xml:space="preserve">track w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">line offset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prev e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Sensors: lateral offset x_i = -2 spacing + i spacing (left &gt; 0); on the line if |x_i - line| &lt; half width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sensor i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x_i (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">|x_i - line|</t>
+  </si>
+  <si>
+    <t xml:space="preserve">on line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. PD steering and wheel speeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active sensors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">error e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de/dt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">omega (rad/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">speed v (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">left wheel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right wheel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate limits (kWheelAccel) and the line-lost search are not modelled here; see followLine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Explosion: colour from temperature, particle motion, debris bounce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: rendering/Effects.cpp bb(T), fire / spark colour; scene/Combat.cpp updateParticles (spark integrator); scene/Scene.cpp updateDebris (restitution). Yellow = constants copied from the code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bb R exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bb G exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bb B gain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bb B exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire life exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emit a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emit b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spark cool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Blackbody ramp bb(T) = (T^a, T^b, k T^c) and fire emission bb(T)(a' + b' T^2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. A flame core and a spark over their lives (t = age / life)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a'+b'T^2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R emit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G emit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B emit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fire T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spark Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bb arg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. One spark, step by step: v_y -= g dt; v *= exp(-k dt); p += v dt; below ground: v_y = -e v_y, v_x *= f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. Debris bounces (restitution e, no drag): apex = v^2 / 2g, flight = 2v / g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drag k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bounce e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keep f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v_x0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v_y0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v0 (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rest below</t>
+  </si>
+  <si>
+    <t xml:space="preserve">step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v_x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v_y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bounce n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v_n (m/s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">apex (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flight (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moving?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total time</t>
   </si>
   <si>
     <t xml:space="preserve">Duty_Cycle: 24-hour roster of the 8 on-duty soldiers (2 shifts, not 6-hour shifts)</t>
@@ -2788,13 +3151,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="0.00E+00"/>
     <numFmt numFmtId="168" formatCode="0.00"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -2948,7 +3312,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3059,6 +3423,10 @@
     </xf>
     <xf numFmtId="168" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -3545,11 +3913,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="46558572"/>
-        <c:axId val="91581063"/>
+        <c:axId val="20858197"/>
+        <c:axId val="98427593"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46558572"/>
+        <c:axId val="20858197"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3582,7 +3950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91581063"/>
+        <c:crossAx val="98427593"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3590,7 +3958,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="91581063"/>
+        <c:axId val="98427593"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3666,7 +4034,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46558572"/>
+        <c:crossAx val="20858197"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4744,6 +5112,3088 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:U42"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="2" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="D6" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>9.21</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="21" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>852</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>854</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <f aca="false">$B$6</f>
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^4/4</f>
+        <v>5.625E-005</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^3/2</f>
+        <v>0.001125</v>
+      </c>
+      <c r="P9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="12" t="n">
+        <f aca="false">C9*H9+D9*H10+E9*H11+F9*H12</f>
+        <v>0.31</v>
+      </c>
+      <c r="S9" s="12" t="n">
+        <f aca="false">C9*I9+D9*I10+E9*I11+F9*I12</f>
+        <v>0</v>
+      </c>
+      <c r="T9" s="12" t="n">
+        <f aca="false">C9*J9+D9*J10+E9*J11+F9*J12</f>
+        <v>0.15</v>
+      </c>
+      <c r="U9" s="12" t="n">
+        <f aca="false">C9*K9+D9*K10+E9*K11+F9*K12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <f aca="false">$B$6</f>
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^4/4</f>
+        <v>5.625E-005</v>
+      </c>
+      <c r="O10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^3/2</f>
+        <v>0.001125</v>
+      </c>
+      <c r="R10" s="12" t="n">
+        <f aca="false">C10*H9+D10*H10+E10*H11+F10*H12</f>
+        <v>0</v>
+      </c>
+      <c r="S10" s="12" t="n">
+        <f aca="false">C10*I9+D10*I10+E10*I11+F10*I12</f>
+        <v>0.31</v>
+      </c>
+      <c r="T10" s="12" t="n">
+        <f aca="false">C10*J9+D10*J10+E10*J11+F10*J12</f>
+        <v>0</v>
+      </c>
+      <c r="U10" s="12" t="n">
+        <f aca="false">C10*K9+D10*K10+E10*K11+F10*K12</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^3/2</f>
+        <v>0.001125</v>
+      </c>
+      <c r="N11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^2</f>
+        <v>0.0225</v>
+      </c>
+      <c r="P11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <f aca="false">C11*H9+D11*H10+E11*H11+F11*H12</f>
+        <v>0.1</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <f aca="false">C11*I9+D11*I10+E11*I11+F11*I12</f>
+        <v>0</v>
+      </c>
+      <c r="T11" s="12" t="n">
+        <f aca="false">C11*J9+D11*J10+E11*J11+F11*J12</f>
+        <v>0.5</v>
+      </c>
+      <c r="U11" s="12" t="n">
+        <f aca="false">C11*K9+D11*K10+E11*K11+F11*K12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^3/2</f>
+        <v>0.001125</v>
+      </c>
+      <c r="O12" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="12" t="n">
+        <f aca="false">$D$6^2*$B$6^2</f>
+        <v>0.0225</v>
+      </c>
+      <c r="R12" s="12" t="n">
+        <f aca="false">C12*H9+D12*H10+E12*H11+F12*H12</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="12" t="n">
+        <f aca="false">C12*I9+D12*I10+E12*I11+F12*I12</f>
+        <v>0.1</v>
+      </c>
+      <c r="T12" s="12" t="n">
+        <f aca="false">C12*J9+D12*J10+E12*J11+F12*J12</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="12" t="n">
+        <f aca="false">C12*K9+D12*K10+E12*K11+F12*K12</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="12" t="n">
+        <f aca="false">C9*$A$9+D9*$A$10+E9*$A$11+F9*$A$12</f>
+        <v>2.12</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <f aca="false">R9*C9+S9*D9+T9*E9+U9*F9+M9</f>
+        <v>0.32505625</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <f aca="false">R9*C10+S9*D10+T9*E10+U9*F10+N9</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <f aca="false">R9*C11+S9*D11+T9*E11+U9*F11+O9</f>
+        <v>0.151125</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <f aca="false">R9*C12+S9*D12+T9*E12+U9*F12+P9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="n">
+        <f aca="false">C10*$A$9+D10*$A$10+E10*$A$11+F10*$A$12</f>
+        <v>4.96</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <f aca="false">R10*C9+S10*D9+T10*E9+U10*F9+M10</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <f aca="false">R10*C10+S10*D10+T10*E10+U10*F10+N10</f>
+        <v>0.32505625</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <f aca="false">R10*C11+S10*D11+T10*E11+U10*F11+O10</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <f aca="false">R10*C12+S10*D12+T10*E12+U10*F12+P10</f>
+        <v>0.151125</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="n">
+        <f aca="false">C11*$A$9+D11*$A$10+E11*$A$11+F11*$A$12</f>
+        <v>1.2</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <f aca="false">R11*C9+S11*D9+T11*E9+U11*F9+M11</f>
+        <v>0.151125</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <f aca="false">R11*C10+S11*D10+T11*E10+U11*F10+N11</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <f aca="false">R11*C11+S11*D11+T11*E11+U11*F11+O11</f>
+        <v>0.5225</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <f aca="false">R11*C12+S11*D12+T11*E12+U11*F12+P11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="n">
+        <f aca="false">C12*$A$9+D12*$A$10+E12*$A$11+F12*$A$12</f>
+        <v>-0.4</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <f aca="false">R12*C9+S12*D9+T12*E9+U12*F9+M12</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <f aca="false">R12*C10+S12*D10+T12*E10+U12*F10+N12</f>
+        <v>0.151125</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <f aca="false">R12*C11+S12*D11+T12*E11+U12*F11+O12</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <f aca="false">R12*C12+S12*D12+T12*E12+U12*F12+P12</f>
+        <v>0.5225</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
+        <v>858</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="B21" s="21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="B22" s="16" t="n">
+        <f aca="false">B21-A15</f>
+        <v>0.38</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <f aca="false">C21-A16</f>
+        <v>-0.36</v>
+      </c>
+      <c r="M22" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N22" s="21" t="n">
+        <v>130</v>
+      </c>
+      <c r="O22" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P22" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q22" s="21" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>868</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>869</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>870</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="12" t="n">
+        <f aca="false">C15+$I$6^2</f>
+        <v>0.57505625</v>
+      </c>
+      <c r="B24" s="12" t="n">
+        <f aca="false">D15</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <f aca="false">B25/(A24*B25-B24*A25)</f>
+        <v>1.73896031909922</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <f aca="false">-B24/(A24*B25-B24*A25)</f>
+        <v>-0</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <f aca="false">C15*D24+D15*D25</f>
+        <v>0.565259920225195</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <f aca="false">C15*E24+D15*E25</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <f aca="false">A15+G24*B22+H24*C22</f>
+        <v>2.33479876968557</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="O24" s="16" t="n">
+        <f aca="false">MAX(0,N24-$Q$22)</f>
+        <v>17.5</v>
+      </c>
+      <c r="P24" s="16" t="n">
+        <f aca="false">0.5*($M$22+$P$22)*$O$22</f>
+        <v>13.6</v>
+      </c>
+      <c r="Q24" s="16" t="n">
+        <f aca="false">IF(O24&lt;=P24,(-$M$22+SQRT($M$22^2+2*$N$22*O24))/$N$22,$O$22+(O24-P24)/$P$22)</f>
+        <v>0.465</v>
+      </c>
+      <c r="R24" s="16" t="n">
+        <f aca="false">MAX(Q24,Q25)-Q24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="n">
+        <f aca="false">C16</f>
+        <v>0</v>
+      </c>
+      <c r="B25" s="12" t="n">
+        <f aca="false">D16+$I$6^2</f>
+        <v>0.57505625</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <f aca="false">-A25/(A24*B25-B24*A25)</f>
+        <v>-0</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <f aca="false">A24/(A24*B25-B24*A25)</f>
+        <v>1.73896031909922</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <f aca="false">C16*D24+D16*D25</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <f aca="false">C16*E24+D16*E25</f>
+        <v>0.565259920225195</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <f aca="false">A16+G25*B22+H25*C22</f>
+        <v>4.75650642871893</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="O25" s="16" t="n">
+        <f aca="false">MAX(0,N25-$Q$22)</f>
+        <v>8.5</v>
+      </c>
+      <c r="P25" s="16" t="n">
+        <f aca="false">0.5*($M$22+$P$22)*$O$22</f>
+        <v>13.6</v>
+      </c>
+      <c r="Q25" s="16" t="n">
+        <f aca="false">IF(O25&lt;=P25,(-$M$22+SQRT($M$22^2+2*$N$22*O25))/$N$22,$O$22+(O25-P25)/$P$22)</f>
+        <v>0.305280585155888</v>
+      </c>
+      <c r="R25" s="16" t="n">
+        <f aca="false">MAX(Q24,Q25)-Q25</f>
+        <v>0.159719414844112</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G26" s="12" t="n">
+        <f aca="false">C17*D24+D17*D25</f>
+        <v>0.262800378223869</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <f aca="false">C17*E24+D17*E25</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <f aca="false">A17+G26*B22+H26*C22</f>
+        <v>1.29986414372507</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <f aca="false">B22*(D24*B22+E24*C22)+C22*(D25*B22+E25*C22)</f>
+        <v>0.476475127433186</v>
+      </c>
+      <c r="D27" s="12" t="str">
+        <f aca="false">IF(C27&lt;$F$6,"inside gate","rejected")</f>
+        <v>inside gate</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <f aca="false">C18*D24+D18*D25</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <f aca="false">C18*E24+D18*E25</f>
+        <v>0.262800378223869</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <f aca="false">A18+G27*B22+H27*C22</f>
+        <v>-0.494608136160593</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="B32" s="21" t="n">
+        <v>-6</v>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="B33" s="21" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C33" s="21" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D33" s="21" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="B34" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" s="21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="B35" s="21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C35" s="21" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D35" s="21" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="B36" s="16" t="n">
+        <f aca="false">($B$33*$B$33+$C$33*$C$33+$D$33*$D$33)</f>
+        <v>0.815</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <f aca="false">($B$33*$B$35+$C$33*$C$35+$D$33*$D$35)</f>
+        <v>0.132</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <f aca="false">($B$35*$B$35+$C$35*$C$35+$D$35*$D$35)</f>
+        <v>0.7749</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="H36" s="16" t="n">
+        <f aca="false">($B$33*($B$32-$B$34)+$C$33*($C$32-$C$34)+$D$33*($D$32-$D$34))</f>
+        <v>-7.2</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <f aca="false">($B$35*($B$32-$B$34)+$C$35*($C$32-$C$34)+$D$35*($D$32-$D$34))</f>
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="B37" s="16" t="n">
+        <f aca="false">($D$36*$J$36-$F$36*$H$36)/($B$36*$F$36-$D$36^2)</f>
+        <v>10.9657485228852</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <f aca="false">($B$36*$J$36-$D$36*$H$36)/($B$36*$F$36-$D$36^2)</f>
+        <v>13.159735198117</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="B39" s="16" t="n">
+        <f aca="false">$B$32+$B$37*$B$33</f>
+        <v>0.031161687586863</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <f aca="false">$C$32+$B$37*$C$33</f>
+        <v>0.323976033980357</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <f aca="false">$D$32+$B$37*$D$33</f>
+        <v>1.64486227843278</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="B40" s="16" t="n">
+        <f aca="false">$B$34+$D$37*$B$35</f>
+        <v>0.420132400941511</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <f aca="false">$C$34+$D$37*$C$35</f>
+        <v>0.446172121223963</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <f aca="false">$D$34+$D$37*$D$35</f>
+        <v>0.788884736602567</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="B41" s="16" t="n">
+        <f aca="false">(B39+B40)/2</f>
+        <v>0.225647044264187</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <f aca="false">(C39+C40)/2</f>
+        <v>0.38507407760216</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <f aca="false">(D39+D40)/2</f>
+        <v>1.21687350751767</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="B42" s="16" t="n">
+        <f aca="false">SQRT((B39-B40)^2+(C39-C40)^2+(D39-D40)^2)</f>
+        <v>0.948117952420988</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G6:H6"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:M26"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="B6" s="28" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0.0166666666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <f aca="false">-2*$B$6+A10*$B$6</f>
+        <v>-0.12</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <f aca="false">ABS(B10-$K$6)</f>
+        <v>0.19</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <f aca="false">IF(C10&lt;$C$6,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">-2*$B$6+A11*$B$6</f>
+        <v>-0.06</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <f aca="false">ABS(B11-$K$6)</f>
+        <v>0.13</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <f aca="false">IF(C11&lt;$C$6,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <f aca="false">-2*$B$6+A12*$B$6</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">ABS(B12-$K$6)</f>
+        <v>0.07</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <f aca="false">IF(C12&lt;$C$6,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <f aca="false">-2*$B$6+A13*$B$6</f>
+        <v>0.06</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">ABS(B13-$K$6)</f>
+        <v>0.01</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <f aca="false">IF(C13&lt;$C$6,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">-2*$B$6+A14*$B$6</f>
+        <v>0.12</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">ABS(B14-$K$6)</f>
+        <v>0.05</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <f aca="false">IF(C14&lt;$C$6,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <f aca="false">SUM(D10:D14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <f aca="false">IF(B17&gt;0,SUMPRODUCT(B10:B14,D10:D14)/B17/$D$6,1)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="B19" s="16" t="n">
+        <f aca="false">(B18-$L$6)/$M$6</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="B20" s="16" t="n">
+        <f aca="false">MAX(-$I$6,MIN($I$6,$E$6*B18+$F$6*B19))</f>
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="B21" s="16" t="n">
+        <f aca="false">$G$6*(1-$H$6*ABS(B18))</f>
+        <v>0.525</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="B22" s="16" t="n">
+        <f aca="false">B21-B20*$J$6/2</f>
+        <v>-0.0625</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="B23" s="16" t="n">
+        <f aca="false">B21+B20*$J$6/2</f>
+        <v>1.1125</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="B24" s="12" t="str">
+        <f aca="false">IF(B20&gt;0,"left",IF(B20&lt;0,"right","straight"))</f>
+        <v>left</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>922</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:S56"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="2" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <f aca="false">A11^$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <f aca="false">A11^$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">$D$7*A11^$E$7</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A11^2</f>
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <f aca="false">B11*E11</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">C11*E11</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <f aca="false">D11*E11</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <f aca="false">(1-J11)^$F$7</f>
+        <v>1</v>
+      </c>
+      <c r="L11" s="16" t="n">
+        <f aca="false">K11^$B$7</f>
+        <v>1</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <f aca="false">K11^$C$7</f>
+        <v>1</v>
+      </c>
+      <c r="N11" s="16" t="n">
+        <f aca="false">$D$7*K11^$E$7</f>
+        <v>0.85</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J11*$I$7))</f>
+        <v>1</v>
+      </c>
+      <c r="P11" s="16" t="n">
+        <f aca="false">0.1+0.9*O11</f>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="16" t="n">
+        <f aca="false">P11^$B$7</f>
+        <v>1</v>
+      </c>
+      <c r="R11" s="16" t="n">
+        <f aca="false">P11^$C$7</f>
+        <v>1</v>
+      </c>
+      <c r="S11" s="16" t="n">
+        <f aca="false">$D$7*P11^$E$7</f>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <f aca="false">A12^$B$7</f>
+        <v>0.354813389233575</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">A12^$C$7</f>
+        <v>0.0125892541179417</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">$D$7*A12^$E$7</f>
+        <v>2.68793601114312E-005</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A12^2</f>
+        <v>0.55</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <f aca="false">B12*E12</f>
+        <v>0.195147364078467</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <f aca="false">C12*E12</f>
+        <v>0.00692408976486792</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <f aca="false">D12*E12</f>
+        <v>1.47836480612872E-005</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <f aca="false">(1-J12)^$F$7</f>
+        <v>0.938740393359569</v>
+      </c>
+      <c r="L12" s="16" t="n">
+        <f aca="false">K12^$B$7</f>
+        <v>0.971953476619273</v>
+      </c>
+      <c r="M12" s="16" t="n">
+        <f aca="false">K12^$C$7</f>
+        <v>0.88682200478731</v>
+      </c>
+      <c r="N12" s="16" t="n">
+        <f aca="false">$D$7*K12^$E$7</f>
+        <v>0.639548818856378</v>
+      </c>
+      <c r="O12" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J12*$I$7))</f>
+        <v>0.91</v>
+      </c>
+      <c r="P12" s="16" t="n">
+        <f aca="false">0.1+0.9*O12</f>
+        <v>0.919</v>
+      </c>
+      <c r="Q12" s="16" t="n">
+        <f aca="false">P12^$B$7</f>
+        <v>0.96270223511889</v>
+      </c>
+      <c r="R12" s="16" t="n">
+        <f aca="false">P12^$C$7</f>
+        <v>0.851725150429171</v>
+      </c>
+      <c r="S12" s="16" t="n">
+        <f aca="false">$D$7*P12^$E$7</f>
+        <v>0.581217560042974</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <f aca="false">A13^$B$7</f>
+        <v>0.484689373328531</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">A13^$C$7</f>
+        <v>0.0469847577235208</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">$D$7*A13^$E$7</f>
+        <v>0.000608210489879943</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A13^2</f>
+        <v>0.7</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">B13*E13</f>
+        <v>0.339282561329972</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">C13*E13</f>
+        <v>0.0328893304064645</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <f aca="false">D13*E13</f>
+        <v>0.00042574734291596</v>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <f aca="false">(1-J13)^$F$7</f>
+        <v>0.874689659154623</v>
+      </c>
+      <c r="L13" s="16" t="n">
+        <f aca="false">K13^$B$7</f>
+        <v>0.941530290453583</v>
+      </c>
+      <c r="M13" s="16" t="n">
+        <f aca="false">K13^$C$7</f>
+        <v>0.775394266129809</v>
+      </c>
+      <c r="N13" s="16" t="n">
+        <f aca="false">$D$7*K13^$E$7</f>
+        <v>0.465330897916165</v>
+      </c>
+      <c r="O13" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J13*$I$7))</f>
+        <v>0.82</v>
+      </c>
+      <c r="P13" s="16" t="n">
+        <f aca="false">0.1+0.9*O13</f>
+        <v>0.838</v>
+      </c>
+      <c r="Q13" s="16" t="n">
+        <f aca="false">P13^$B$7</f>
+        <v>0.923548715002778</v>
+      </c>
+      <c r="R13" s="16" t="n">
+        <f aca="false">P13^$C$7</f>
+        <v>0.714765587887991</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <f aca="false">$D$7*P13^$E$7</f>
+        <v>0.383722274040578</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <f aca="false">A14^$B$7</f>
+        <v>0.581707367927938</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <f aca="false">A14^$C$7</f>
+        <v>0.101515038570495</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <f aca="false">$D$7*A14^$E$7</f>
+        <v>0.00377106980842307</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A14^2</f>
+        <v>0.95</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <f aca="false">B14*E14</f>
+        <v>0.552621999531541</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <f aca="false">C14*E14</f>
+        <v>0.0964392866419702</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <f aca="false">D14*E14</f>
+        <v>0.00358251631800191</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <f aca="false">(1-J14)^$F$7</f>
+        <v>0.807344375447297</v>
+      </c>
+      <c r="L14" s="16" t="n">
+        <f aca="false">K14^$B$7</f>
+        <v>0.908189488058911</v>
+      </c>
+      <c r="M14" s="16" t="n">
+        <f aca="false">K14^$C$7</f>
+        <v>0.665904217674399</v>
+      </c>
+      <c r="N14" s="16" t="n">
+        <f aca="false">$D$7*K14^$E$7</f>
+        <v>0.324476787627242</v>
+      </c>
+      <c r="O14" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J14*$I$7))</f>
+        <v>0.73</v>
+      </c>
+      <c r="P14" s="16" t="n">
+        <f aca="false">0.1+0.9*O14</f>
+        <v>0.757</v>
+      </c>
+      <c r="Q14" s="16" t="n">
+        <f aca="false">P14^$B$7</f>
+        <v>0.882253004006061</v>
+      </c>
+      <c r="R14" s="16" t="n">
+        <f aca="false">P14^$C$7</f>
+        <v>0.589226364849833</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <f aca="false">$D$7*P14^$E$7</f>
+        <v>0.24285686443234</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <f aca="false">A15^$B$7</f>
+        <v>0.662105195987833</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <f aca="false">A15^$C$7</f>
+        <v>0.175353316221635</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <f aca="false">$D$7*A15^$E$7</f>
+        <v>0.0137622323770528</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A15^2</f>
+        <v>1.3</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <f aca="false">B15*E15</f>
+        <v>0.860736754784183</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <f aca="false">C15*E15</f>
+        <v>0.227959311088125</v>
+      </c>
+      <c r="H15" s="16" t="n">
+        <f aca="false">D15*E15</f>
+        <v>0.0178909020901686</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K15" s="16" t="n">
+        <f aca="false">(1-J15)^$F$7</f>
+        <v>0.736021922817833</v>
+      </c>
+      <c r="L15" s="16" t="n">
+        <f aca="false">K15^$B$7</f>
+        <v>0.87116583999998</v>
+      </c>
+      <c r="M15" s="16" t="n">
+        <f aca="false">K15^$C$7</f>
+        <v>0.558589059578594</v>
+      </c>
+      <c r="N15" s="16" t="n">
+        <f aca="false">$D$7*K15^$E$7</f>
+        <v>0.214006666266815</v>
+      </c>
+      <c r="O15" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J15*$I$7))</f>
+        <v>0.64</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <f aca="false">0.1+0.9*O15</f>
+        <v>0.676</v>
+      </c>
+      <c r="Q15" s="16" t="n">
+        <f aca="false">P15^$B$7</f>
+        <v>0.838447768440115</v>
+      </c>
+      <c r="R15" s="16" t="n">
+        <f aca="false">P15^$C$7</f>
+        <v>0.475224390431893</v>
+      </c>
+      <c r="S15" s="16" t="n">
+        <f aca="false">$D$7*P15^$E$7</f>
+        <v>0.145941584613537</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B16" s="16" t="n">
+        <f aca="false">A16^$B$7</f>
+        <v>0.732042847972813</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <f aca="false">A16^$C$7</f>
+        <v>0.267943365634073</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <f aca="false">$D$7*A16^$E$7</f>
+        <v>0.0375650477505353</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A16^2</f>
+        <v>1.75</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <f aca="false">B16*E16</f>
+        <v>1.28107498395242</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <f aca="false">C16*E16</f>
+        <v>0.468900889859628</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <f aca="false">D16*E16</f>
+        <v>0.0657388335634369</v>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <f aca="false">(1-J16)^$F$7</f>
+        <v>0.659753955386447</v>
+      </c>
+      <c r="L16" s="16" t="n">
+        <f aca="false">K16^$B$7</f>
+        <v>0.829319545814442</v>
+      </c>
+      <c r="M16" s="16" t="n">
+        <f aca="false">K16^$C$7</f>
+        <v>0.45375957765858</v>
+      </c>
+      <c r="N16" s="16" t="n">
+        <f aca="false">$D$7*K16^$E$7</f>
+        <v>0.130809093917897</v>
+      </c>
+      <c r="O16" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J16*$I$7))</f>
+        <v>0.55</v>
+      </c>
+      <c r="P16" s="16" t="n">
+        <f aca="false">0.1+0.9*O16</f>
+        <v>0.595</v>
+      </c>
+      <c r="Q16" s="16" t="n">
+        <f aca="false">P16^$B$7</f>
+        <v>0.79164893997207</v>
+      </c>
+      <c r="R16" s="16" t="n">
+        <f aca="false">P16^$C$7</f>
+        <v>0.372891286274547</v>
+      </c>
+      <c r="S16" s="16" t="n">
+        <f aca="false">$D$7*P16^$E$7</f>
+        <v>0.0821760518031618</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <f aca="false">A17^$B$7</f>
+        <v>0.794635682240204</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <f aca="false">A17^$C$7</f>
+        <v>0.378867520493613</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <f aca="false">$D$7*A17^$E$7</f>
+        <v>0.0853295690836418</v>
+      </c>
+      <c r="E17" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A17^2</f>
+        <v>2.3</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <f aca="false">B17*E17</f>
+        <v>1.82766206915247</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <f aca="false">C17*E17</f>
+        <v>0.87139529713531</v>
+      </c>
+      <c r="H17" s="16" t="n">
+        <f aca="false">D17*E17</f>
+        <v>0.196258008892376</v>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K17" s="16" t="n">
+        <f aca="false">(1-J17)^$F$7</f>
+        <v>0.577079962362886</v>
+      </c>
+      <c r="L17" s="16" t="n">
+        <f aca="false">K17^$B$7</f>
+        <v>0.780829472849505</v>
+      </c>
+      <c r="M17" s="16" t="n">
+        <f aca="false">K17^$C$7</f>
+        <v>0.351842574717947</v>
+      </c>
+      <c r="N17" s="16" t="n">
+        <f aca="false">$D$7*K17^$E$7</f>
+        <v>0.0716111919157826</v>
+      </c>
+      <c r="O17" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J17*$I$7))</f>
+        <v>0.46</v>
+      </c>
+      <c r="P17" s="16" t="n">
+        <f aca="false">0.1+0.9*O17</f>
+        <v>0.514</v>
+      </c>
+      <c r="Q17" s="16" t="n">
+        <f aca="false">P17^$B$7</f>
+        <v>0.741196574540104</v>
+      </c>
+      <c r="R17" s="16" t="n">
+        <f aca="false">P17^$C$7</f>
+        <v>0.282377394124532</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <f aca="false">$D$7*P17^$E$7</f>
+        <v>0.0425356389734444</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <f aca="false">A18^$B$7</f>
+        <v>0.851714651122792</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <f aca="false">A18^$C$7</f>
+        <v>0.507792492856054</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <f aca="false">$D$7*A18^$E$7</f>
+        <v>0.170749761515207</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A18^2</f>
+        <v>2.95</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <f aca="false">B18*E18</f>
+        <v>2.51255822081224</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <f aca="false">C18*E18</f>
+        <v>1.49798785392536</v>
+      </c>
+      <c r="H18" s="16" t="n">
+        <f aca="false">D18*E18</f>
+        <v>0.50371179646986</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K18" s="16" t="n">
+        <f aca="false">(1-J18)^$F$7</f>
+        <v>0.485593374830204</v>
+      </c>
+      <c r="L18" s="16" t="n">
+        <f aca="false">K18^$B$7</f>
+        <v>0.72247485875784</v>
+      </c>
+      <c r="M18" s="16" t="n">
+        <f aca="false">K18^$C$7</f>
+        <v>0.253465135759087</v>
+      </c>
+      <c r="N18" s="16" t="n">
+        <f aca="false">$D$7*K18^$E$7</f>
+        <v>0.03293413894912</v>
+      </c>
+      <c r="O18" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J18*$I$7))</f>
+        <v>0.37</v>
+      </c>
+      <c r="P18" s="16" t="n">
+        <f aca="false">0.1+0.9*O18</f>
+        <v>0.433</v>
+      </c>
+      <c r="Q18" s="16" t="n">
+        <f aca="false">P18^$B$7</f>
+        <v>0.686150767339576</v>
+      </c>
+      <c r="R18" s="16" t="n">
+        <f aca="false">P18^$C$7</f>
+        <v>0.203857645100459</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <f aca="false">$D$7*P18^$E$7</f>
+        <v>0.0196614009302285</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B19" s="16" t="n">
+        <f aca="false">A19^$B$7</f>
+        <v>0.904462351925639</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">A19^$C$7</f>
+        <v>0.654441716840687</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <f aca="false">$D$7*A19^$E$7</f>
+        <v>0.311403770818531</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A19^2</f>
+        <v>3.7</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <f aca="false">B19*E19</f>
+        <v>3.34651070212487</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <f aca="false">C19*E19</f>
+        <v>2.42143435231054</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <f aca="false">D19*E19</f>
+        <v>1.15219395202856</v>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K19" s="16" t="n">
+        <f aca="false">(1-J19)^$F$7</f>
+        <v>0.380730787743176</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <f aca="false">K19^$B$7</f>
+        <v>0.647557143782081</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <f aca="false">K19^$C$7</f>
+        <v>0.159651938106323</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <f aca="false">$D$7*K19^$E$7</f>
+        <v>0.0110204648575108</v>
+      </c>
+      <c r="O19" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J19*$I$7))</f>
+        <v>0.28</v>
+      </c>
+      <c r="P19" s="16" t="n">
+        <f aca="false">0.1+0.9*O19</f>
+        <v>0.352</v>
+      </c>
+      <c r="Q19" s="16" t="n">
+        <f aca="false">P19^$B$7</f>
+        <v>0.625092371027076</v>
+      </c>
+      <c r="R19" s="16" t="n">
+        <f aca="false">P19^$C$7</f>
+        <v>0.137540646255321</v>
+      </c>
+      <c r="S19" s="16" t="n">
+        <f aca="false">$D$7*P19^$E$7</f>
+        <v>0.00774213805735474</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B20" s="16" t="n">
+        <f aca="false">A20^$B$7</f>
+        <v>0.953694173245785</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <f aca="false">A20^$C$7</f>
+        <v>0.818579318474666</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <f aca="false">$D$7*A20^$E$7</f>
+        <v>0.529066445073301</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A20^2</f>
+        <v>4.55</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <f aca="false">B20*E20</f>
+        <v>4.33930848826832</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <f aca="false">C20*E20</f>
+        <v>3.72453589905973</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <f aca="false">D20*E20</f>
+        <v>2.40725232508352</v>
+      </c>
+      <c r="J20" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K20" s="16" t="n">
+        <f aca="false">(1-J20)^$F$7</f>
+        <v>0.251188643150958</v>
+      </c>
+      <c r="L20" s="16" t="n">
+        <f aca="false">K20^$B$7</f>
+        <v>0.537031796370253</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <f aca="false">K20^$C$7</f>
+        <v>0.072443596007499</v>
+      </c>
+      <c r="N20" s="16" t="n">
+        <f aca="false">$D$7*K20^$E$7</f>
+        <v>0.00169597296772355</v>
+      </c>
+      <c r="O20" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J20*$I$7))</f>
+        <v>0.19</v>
+      </c>
+      <c r="P20" s="16" t="n">
+        <f aca="false">0.1+0.9*O20</f>
+        <v>0.271</v>
+      </c>
+      <c r="Q20" s="16" t="n">
+        <f aca="false">P20^$B$7</f>
+        <v>0.55569460559631</v>
+      </c>
+      <c r="R20" s="16" t="n">
+        <f aca="false">P20^$C$7</f>
+        <v>0.0836838500606752</v>
+      </c>
+      <c r="S20" s="16" t="n">
+        <f aca="false">$D$7*P20^$E$7</f>
+        <v>0.00238660603588605</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="16" t="n">
+        <f aca="false">A21^$B$7</f>
+        <v>1</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <f aca="false">A21^$C$7</f>
+        <v>1</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <f aca="false">$D$7*A21^$E$7</f>
+        <v>0.85</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <f aca="false">$G$7+$H$7*A21^2</f>
+        <v>5.5</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <f aca="false">B21*E21</f>
+        <v>5.5</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <f aca="false">C21*E21</f>
+        <v>5.5</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <f aca="false">D21*E21</f>
+        <v>4.675</v>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="16" t="n">
+        <f aca="false">(1-J21)^$F$7</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="16" t="n">
+        <f aca="false">K21^$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="16" t="n">
+        <f aca="false">K21^$C$7</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="16" t="n">
+        <f aca="false">$D$7*K21^$E$7</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="16" t="n">
+        <f aca="false">MAX(0,MIN(1,1-J21*$I$7))</f>
+        <v>0.1</v>
+      </c>
+      <c r="P21" s="16" t="n">
+        <f aca="false">0.1+0.9*O21</f>
+        <v>0.19</v>
+      </c>
+      <c r="Q21" s="16" t="n">
+        <f aca="false">P21^$B$7</f>
+        <v>0.473629909893885</v>
+      </c>
+      <c r="R21" s="16" t="n">
+        <f aca="false">P21^$C$7</f>
+        <v>0.042621805393757</v>
+      </c>
+      <c r="S21" s="16" t="n">
+        <f aca="false">$D$7*P21^$E$7</f>
+        <v>0.00048284765883799</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>942</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="B26" s="21" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="C26" s="21" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K26" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" s="21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M26" s="21" t="n">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <f aca="false">$I$26</f>
+        <v>1</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <f aca="false">$G$26</f>
+        <v>11</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <f aca="false">$H$26</f>
+        <v>6</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="16" t="n">
+        <f aca="false">$K$26*$J$26^J28</f>
+        <v>5</v>
+      </c>
+      <c r="L28" s="16" t="n">
+        <f aca="false">K28^2/(2*$M$26)</f>
+        <v>1.27420998980632</v>
+      </c>
+      <c r="M28" s="16" t="n">
+        <f aca="false">2*K28/$M$26</f>
+        <v>1.01936799184506</v>
+      </c>
+      <c r="N28" s="12" t="str">
+        <f aca="false">IF(K28&gt;=$L$26,"yes","rest")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="16" t="n">
+        <f aca="false">B28+$F$26</f>
+        <v>0.05</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <f aca="false">C28+E28*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>0.539109270318716</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <f aca="false">MAX(0.02,(D28+(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.27002022952918</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <f aca="false">IF((D28+(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E28*EXP(-$C$26*$F$26)*$E$26,E28*EXP(-$C$26*$F$26))</f>
+        <v>10.7821854063743</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <f aca="false">IF((D28+(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F28-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F28-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>5.40040459058357</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="16" t="n">
+        <f aca="false">$K$26*$J$26^J29</f>
+        <v>1.5</v>
+      </c>
+      <c r="L29" s="16" t="n">
+        <f aca="false">K29^2/(2*$M$26)</f>
+        <v>0.114678899082569</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <f aca="false">2*K29/$M$26</f>
+        <v>0.305810397553517</v>
+      </c>
+      <c r="N29" s="12" t="str">
+        <f aca="false">IF(K29&gt;=$L$26,"yes","rest")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="16" t="n">
+        <f aca="false">B29+$F$26</f>
+        <v>0.1</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <f aca="false">C29+E29*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>1.06754346185249</v>
+      </c>
+      <c r="D30" s="16" t="n">
+        <f aca="false">MAX(0.02,(D29+(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.51065432781682</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <f aca="false">IF((D29+(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E29*EXP(-$C$26*$F$26)*$E$26,E29*EXP(-$C$26*$F$26))</f>
+        <v>10.5686838306756</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <f aca="false">IF((D29+(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F29-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F29-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>4.81268196575276</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="16" t="n">
+        <f aca="false">$K$26*$J$26^J30</f>
+        <v>0.45</v>
+      </c>
+      <c r="L30" s="16" t="n">
+        <f aca="false">K30^2/(2*$M$26)</f>
+        <v>0.0103211009174312</v>
+      </c>
+      <c r="M30" s="16" t="n">
+        <f aca="false">2*K30/$M$26</f>
+        <v>0.091743119266055</v>
+      </c>
+      <c r="N30" s="12" t="str">
+        <f aca="false">IF(K30&gt;=$L$26,"yes","rest")</f>
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="16" t="n">
+        <f aca="false">B30+$F$26</f>
+        <v>0.15</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <f aca="false">C30+E30*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>1.58551395532383</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <f aca="false">MAX(0.02,(D30+(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.72248417924788</v>
+      </c>
+      <c r="E31" s="16" t="n">
+        <f aca="false">IF((D30+(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E30*EXP(-$C$26*$F$26)*$E$26,E30*EXP(-$C$26*$F$26))</f>
+        <v>10.3594098694267</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <f aca="false">IF((D30+(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F30-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F30-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>4.23659702862124</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="16" t="n">
+        <f aca="false">$K$26*$J$26^J31</f>
+        <v>0.135</v>
+      </c>
+      <c r="L31" s="16" t="n">
+        <f aca="false">K31^2/(2*$M$26)</f>
+        <v>0.000928899082568807</v>
+      </c>
+      <c r="M31" s="16" t="n">
+        <f aca="false">2*K31/$M$26</f>
+        <v>0.0275229357798165</v>
+      </c>
+      <c r="N31" s="12" t="str">
+        <f aca="false">IF(K31&gt;=$L$26,"yes","rest")</f>
+        <v>rest</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="16" t="n">
+        <f aca="false">B31+$F$26</f>
+        <v>0.2</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <f aca="false">C31+E31*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>2.09322794583648</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <f aca="false">MAX(0.02,(D31+(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.90608014612452</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <f aca="false">IF((D31+(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E31*EXP(-$C$26*$F$26)*$E$26,E31*EXP(-$C$26*$F$26))</f>
+        <v>10.154279810253</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <f aca="false">IF((D31+(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F31-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F31-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>3.67191933753292</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="16" t="n">
+        <f aca="false">$K$26*$J$26^J32</f>
+        <v>0.0405</v>
+      </c>
+      <c r="L32" s="16" t="n">
+        <f aca="false">K32^2/(2*$M$26)</f>
+        <v>8.36009174311926E-005</v>
+      </c>
+      <c r="M32" s="16" t="n">
+        <f aca="false">2*K32/$M$26</f>
+        <v>0.00825688073394495</v>
+      </c>
+      <c r="N32" s="12" t="str">
+        <f aca="false">IF(K32&gt;=$L$26,"yes","rest")</f>
+        <v>rest</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="16" t="n">
+        <f aca="false">B32+$F$26</f>
+        <v>0.25</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <f aca="false">C32+E32*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>2.59088852575626</v>
+      </c>
+      <c r="D33" s="16" t="n">
+        <f aca="false">MAX(0.02,(D32+(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.06200129681864</v>
+      </c>
+      <c r="E33" s="16" t="n">
+        <f aca="false">IF((D32+(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E32*EXP(-$C$26*$F$26)*$E$26,E32*EXP(-$C$26*$F$26))</f>
+        <v>9.95321159839555</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <f aca="false">IF((D32+(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F32-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F32-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>3.11842301388222</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="16" t="n">
+        <f aca="false">$K$26*$J$26^J33</f>
+        <v>0.01215</v>
+      </c>
+      <c r="L33" s="16" t="n">
+        <f aca="false">K33^2/(2*$M$26)</f>
+        <v>7.52408256880734E-006</v>
+      </c>
+      <c r="M33" s="16" t="n">
+        <f aca="false">2*K33/$M$26</f>
+        <v>0.00247706422018349</v>
+      </c>
+      <c r="N33" s="12" t="str">
+        <f aca="false">IF(K33&gt;=$L$26,"yes","rest")</f>
+        <v>rest</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="16" t="n">
+        <f aca="false">B33+$F$26</f>
+        <v>0.3</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <f aca="false">C33+E33*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>3.07869476595069</v>
+      </c>
+      <c r="D34" s="16" t="n">
+        <f aca="false">MAX(0.02,(D33+(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.19079562940662</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <f aca="false">IF((D33+(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E33*EXP(-$C$26*$F$26)*$E$26,E33*EXP(-$C$26*$F$26))</f>
+        <v>9.75612480388873</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <f aca="false">IF((D33+(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F33-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F33-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>2.57588665175964</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="16" t="n">
+        <f aca="false">B34+$F$26</f>
+        <v>0.35</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <f aca="false">C34+E34*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>3.55684179542004</v>
+      </c>
+      <c r="D35" s="16" t="n">
+        <f aca="false">MAX(0.02,(D34+(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.29300029087594</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <f aca="false">IF((D34+(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E34*EXP(-$C$26*$F$26)*$E$26,E34*EXP(-$C$26*$F$26))</f>
+        <v>9.56294058938686</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <f aca="false">IF((D34+(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F34-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F34-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>2.04409322938642</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="M35" s="16" t="n">
+        <f aca="false">SUMIF(N28:N33,"yes",M28:M33)</f>
+        <v>1.41692150866463</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="16" t="n">
+        <f aca="false">B35+$F$26</f>
+        <v>0.4</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <f aca="false">C35+E35*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>4.02552087935145</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <f aca="false">MAX(0.02,(D35+(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.36914179199108</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <f aca="false">IF((D35+(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E35*EXP(-$C$26*$F$26)*$E$26,E35*EXP(-$C$26*$F$26))</f>
+        <v>9.37358167862832</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <f aca="false">IF((D35+(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F35-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F35-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>1.52283002230293</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" s="16" t="n">
+        <f aca="false">B36+$F$26</f>
+        <v>0.45</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <f aca="false">C36+E36*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>4.48491949562765</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <f aca="false">MAX(0.02,(D36+(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.41973621790489</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <f aca="false">IF((D36+(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E36*EXP(-$C$26*$F$26)*$E$26,E36*EXP(-$C$26*$F$26))</f>
+        <v>9.18797232552399</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <f aca="false">IF((D36+(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F36-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F36-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>1.01188851827606</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B38" s="16" t="n">
+        <f aca="false">B37+$F$26</f>
+        <v>0.5</v>
+      </c>
+      <c r="C38" s="16" t="n">
+        <f aca="false">C37+E37*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>4.93522140982054</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <f aca="false">MAX(0.02,(D37+(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.44528943459947</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <f aca="false">IF((D37+(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E37*EXP(-$C$26*$F$26)*$E$26,E37*EXP(-$C$26*$F$26))</f>
+        <v>9.0060382838578</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <f aca="false">IF((D37+(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F37-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F37-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>0.511064333891569</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" s="16" t="n">
+        <f aca="false">B38+$F$26</f>
+        <v>0.55</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <f aca="false">C38+E38*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>5.37660674869991</v>
+      </c>
+      <c r="D39" s="16" t="n">
+        <f aca="false">MAX(0.02,(D38+(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.44629729123936</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <f aca="false">IF((D38+(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E38*EXP(-$C$26*$F$26)*$E$26,E38*EXP(-$C$26*$F$26))</f>
+        <v>8.82770677758726</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <f aca="false">IF((D38+(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F38-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F38-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>0.0201571327979528</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B40" s="16" t="n">
+        <f aca="false">B39+$F$26</f>
+        <v>0.6</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <f aca="false">C39+E39*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>5.80925207228651</v>
+      </c>
+      <c r="D40" s="16" t="n">
+        <f aca="false">MAX(0.02,(D39+(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.42324581851783</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <f aca="false">IF((D39+(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E39*EXP(-$C$26*$F$26)*$E$26,E39*EXP(-$C$26*$F$26))</f>
+        <v>8.65290647173208</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <f aca="false">IF((D39+(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F39-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F39-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-0.461029454430742</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" s="16" t="n">
+        <f aca="false">B40+$F$26</f>
+        <v>0.65</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <f aca="false">C40+E40*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>6.23333044447847</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <f aca="false">MAX(0.02,(D40+(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.37661142307556</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <f aca="false">IF((D40+(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E40*EXP(-$C$26*$F$26)*$E$26,E40*EXP(-$C$26*$F$26))</f>
+        <v>8.48156744383922</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <f aca="false">IF((D40+(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F40-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F40-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-0.932687908845314</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B42" s="16" t="n">
+        <f aca="false">B41+$F$26</f>
+        <v>0.7</v>
+      </c>
+      <c r="C42" s="16" t="n">
+        <f aca="false">C41+E41*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>6.64901150227912</v>
+      </c>
+      <c r="D42" s="16" t="n">
+        <f aca="false">MAX(0.02,(D41+(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.30686107806974</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <f aca="false">IF((D41+(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E41*EXP(-$C$26*$F$26)*$E$26,E41*EXP(-$C$26*$F$26))</f>
+        <v>8.31362115601297</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <f aca="false">IF((D41+(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F41-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F41-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-1.39500690011639</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B43" s="16" t="n">
+        <f aca="false">B42+$F$26</f>
+        <v>0.75</v>
+      </c>
+      <c r="C43" s="16" t="n">
+        <f aca="false">C42+E42*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>7.05646152365407</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <f aca="false">MAX(0.02,(D42+(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.2144525099695</v>
+      </c>
+      <c r="E43" s="16" t="n">
+        <f aca="false">IF((D42+(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E42*EXP(-$C$26*$F$26)*$E$26,E42*EXP(-$C$26*$F$26))</f>
+        <v>8.14900042749889</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <f aca="false">IF((D42+(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F42-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F42-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-1.84817136200482</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B44" s="16" t="n">
+        <f aca="false">B43+$F$26</f>
+        <v>0.8</v>
+      </c>
+      <c r="C44" s="16" t="n">
+        <f aca="false">C43+E43*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>7.45584349404459</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <f aca="false">MAX(0.02,(D43+(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>2.09983438165262</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <f aca="false">IF((D43+(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E43*EXP(-$C$26*$F$26)*$E$26,E43*EXP(-$C$26*$F$26))</f>
+        <v>7.98763940781059</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <f aca="false">IF((D43+(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F43-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F43-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-2.29236256633763</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B45" s="16" t="n">
+        <f aca="false">B44+$F$26</f>
+        <v>0.85</v>
+      </c>
+      <c r="C45" s="16" t="n">
+        <f aca="false">C44+E44*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>7.84731717156403</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <f aca="false">MAX(0.02,(D44+(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.96344647187666</v>
+      </c>
+      <c r="E45" s="16" t="n">
+        <f aca="false">IF((D44+(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E44*EXP(-$C$26*$F$26)*$E$26,E44*EXP(-$C$26*$F$26))</f>
+        <v>7.8294735503887</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <f aca="false">IF((D44+(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F44-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F44-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-2.72775819551917</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B46" s="16" t="n">
+        <f aca="false">B45+$F$26</f>
+        <v>0.9</v>
+      </c>
+      <c r="C46" s="16" t="n">
+        <f aca="false">C45+E45*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>8.2310391509031</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <f aca="false">MAX(0.02,(D45+(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.80571985119634</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <f aca="false">IF((D45+(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E45*EXP(-$C$26*$F$26)*$E$26,E45*EXP(-$C$26*$F$26))</f>
+        <v>7.67443958678133</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <f aca="false">IF((D45+(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F45-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F45-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-3.15453241360649</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B47" s="16" t="n">
+        <f aca="false">B46+$F$26</f>
+        <v>0.95</v>
+      </c>
+      <c r="C47" s="16" t="n">
+        <f aca="false">C46+E46*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>8.60716292596989</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <f aca="false">MAX(0.02,(D46+(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.62707705439748</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <f aca="false">IF((D46+(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E46*EXP(-$C$26*$F$26)*$E$26,E46*EXP(-$C$26*$F$26))</f>
+        <v>7.52247550133591</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <f aca="false">IF((D46+(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F46-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F46-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-3.5728559359772</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B48" s="16" t="n">
+        <f aca="false">B47+$F$26</f>
+        <v>1</v>
+      </c>
+      <c r="C48" s="16" t="n">
+        <f aca="false">C47+E47*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>8.97583895128949</v>
+      </c>
+      <c r="D48" s="16" t="n">
+        <f aca="false">MAX(0.02,(D47+(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.42793224951658</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <f aca="false">IF((D47+(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E47*EXP(-$C$26*$F$26)*$E$26,E47*EXP(-$C$26*$F$26))</f>
+        <v>7.37352050639202</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <f aca="false">IF((D47+(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F47-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F47-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-3.98289609761798</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B49" s="16" t="n">
+        <f aca="false">B48+$F$26</f>
+        <v>1.05</v>
+      </c>
+      <c r="C49" s="16" t="n">
+        <f aca="false">C48+E48*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>9.33721470218777</v>
+      </c>
+      <c r="D49" s="16" t="n">
+        <f aca="false">MAX(0.02,(D48+(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>1.20869140351354</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <f aca="false">IF((D48+(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E48*EXP(-$C$26*$F$26)*$E$26,E48*EXP(-$C$26*$F$26))</f>
+        <v>7.22751501796562</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <f aca="false">IF((D48+(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F48-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F48-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-4.38481692006076</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B50" s="16" t="n">
+        <f aca="false">B49+$F$26</f>
+        <v>1.1</v>
+      </c>
+      <c r="C50" s="16" t="n">
+        <f aca="false">C49+E49*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>9.6914347337835</v>
+      </c>
+      <c r="D50" s="16" t="n">
+        <f aca="false">MAX(0.02,(D49+(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>0.969752444663863</v>
+      </c>
+      <c r="E50" s="16" t="n">
+        <f aca="false">IF((D49+(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E49*EXP(-$C$26*$F$26)*$E$26,E49*EXP(-$C$26*$F$26))</f>
+        <v>7.08440063191455</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <f aca="false">IF((D49+(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F49-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F49-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-4.77877917699353</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B51" s="16" t="n">
+        <f aca="false">B50+$F$26</f>
+        <v>1.15</v>
+      </c>
+      <c r="C51" s="16" t="n">
+        <f aca="false">C50+E50*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>10.0386407388123</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <f aca="false">MAX(0.02,(D50+(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>0.711505421735265</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <f aca="false">IF((D50+(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E50*EXP(-$C$26*$F$26)*$E$26,E50*EXP(-$C$26*$F$26))</f>
+        <v>6.94412010057618</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <f aca="false">IF((D50+(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F50-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F50-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-5.16494045857197</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B52" s="16" t="n">
+        <f aca="false">B51+$F$26</f>
+        <v>1.2</v>
+      </c>
+      <c r="C52" s="16" t="n">
+        <f aca="false">C51+E51*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>10.3789716043057</v>
+      </c>
+      <c r="D52" s="16" t="n">
+        <f aca="false">MAX(0.02,(D51+(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>0.434332660012385</v>
+      </c>
+      <c r="E52" s="16" t="n">
+        <f aca="false">IF((D51+(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E51*EXP(-$C$26*$F$26)*$E$26,E51*EXP(-$C$26*$F$26))</f>
+        <v>6.80661730986754</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <f aca="false">IF((D51+(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F51-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F51-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-5.54345523445759</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B53" s="16" t="n">
+        <f aca="false">B52+$F$26</f>
+        <v>1.25</v>
+      </c>
+      <c r="C53" s="16" t="n">
+        <f aca="false">C52+E52*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>10.7125634671476</v>
+      </c>
+      <c r="D53" s="16" t="n">
+        <f aca="false">MAX(0.02,(D52+(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>0.138608914232001</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <f aca="false">IF((D52+(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E52*EXP(-$C$26*$F$26)*$E$26,E52*EXP(-$C$26*$F$26))</f>
+        <v>6.67183725683896</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <f aca="false">IF((D52+(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F52-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F52-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>-5.91447491560768</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B54" s="16" t="n">
+        <f aca="false">B53+$F$26</f>
+        <v>1.3</v>
+      </c>
+      <c r="C54" s="16" t="n">
+        <f aca="false">C53+E53*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>11.0395497685312</v>
+      </c>
+      <c r="D54" s="16" t="n">
+        <f aca="false">MAX(0.02,(D53+(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>0.02</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <f aca="false">IF((D53+(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E53*EXP(-$C$26*$F$26)*$E$26,E53*EXP(-$C$26*$F$26))</f>
+        <v>3.92383561660328</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <f aca="false">IF((D53+(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F53-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F53-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>1.56953697871042</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B55" s="16" t="n">
+        <f aca="false">B54+$F$26</f>
+        <v>1.35</v>
+      </c>
+      <c r="C55" s="16" t="n">
+        <f aca="false">C54+E54*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>11.2318566918147</v>
+      </c>
+      <c r="D55" s="16" t="n">
+        <f aca="false">MAX(0.02,(D54+(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>0.0728835307490444</v>
+      </c>
+      <c r="E55" s="16" t="n">
+        <f aca="false">IF((D54+(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E54*EXP(-$C$26*$F$26)*$E$26,E54*EXP(-$C$26*$F$26))</f>
+        <v>3.84613846566833</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <f aca="false">IF((D54+(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F54-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F54-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>1.05767061498089</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B56" s="16" t="n">
+        <f aca="false">B55+$F$26</f>
+        <v>1.4</v>
+      </c>
+      <c r="C56" s="16" t="n">
+        <f aca="false">C55+E55*EXP(-$C$26*$F$26)*$F$26</f>
+        <v>11.4203556828848</v>
+      </c>
+      <c r="D56" s="16" t="n">
+        <f aca="false">MAX(0.02,(D55+(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26))</f>
+        <v>0.100680524966187</v>
+      </c>
+      <c r="E56" s="16" t="n">
+        <f aca="false">IF((D55+(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,E55*EXP(-$C$26*$F$26)*$E$26,E55*EXP(-$C$26*$F$26))</f>
+        <v>3.76997982140217</v>
+      </c>
+      <c r="F56" s="16" t="n">
+        <f aca="false">IF((D55+(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$F$26)&lt;0.02,-(F55-$B$26*$F$26)*EXP(-$C$26*$F$26)*$D$26,(F55-$B$26*$F$26)*EXP(-$C$26*$F$26))</f>
+        <v>0.555939884342843</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="80" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4754,7 +8204,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>844</v>
+        <v>963</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4764,26 +8214,26 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>845</v>
+        <v>964</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>846</v>
+        <v>965</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="21" t="n">
         <v>6.4</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>847</v>
+        <v>966</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="21" t="n">
         <v>17.6</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>848</v>
+        <v>967</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="12" t="str">
@@ -4793,23 +8243,23 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="4" t="s">
-        <v>849</v>
+        <v>968</v>
       </c>
       <c r="P5" s="4"/>
-      <c r="Q5" s="28" t="n">
+      <c r="Q5" s="29" t="n">
         <f aca="false">$H$5-$D$5</f>
         <v>11.2</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>850</v>
+        <v>969</v>
       </c>
       <c r="T5" s="4"/>
-      <c r="U5" s="28" t="n">
+      <c r="U5" s="29" t="n">
         <f aca="false">24-($H$5-$D$5)</f>
         <v>12.8</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>851</v>
+        <v>970</v>
       </c>
       <c r="X5" s="4"/>
       <c r="Y5" s="21" t="n">
@@ -4821,13 +8271,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>852</v>
+        <v>971</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>853</v>
+        <v>972</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>854</v>
+        <v>973</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -4841,7 +8291,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>855</v>
+        <v>974</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
@@ -4853,10 +8303,10 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>856</v>
+        <v>975</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>857</v>
+        <v>976</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4864,34 +8314,34 @@
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>858</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>859</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29" t="s">
-        <v>860</v>
-      </c>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
+        <v>977</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>978</v>
+      </c>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30" t="s">
+        <v>979</v>
+      </c>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="30"/>
       <c r="Y8" s="12" t="str">
         <f aca="false">IF(LEFT(C8,FIND(":",C8)-1)="off duty","off",LEFT(C8,FIND(":",C8)-1))</f>
         <v>guard</v>
@@ -4906,34 +8356,34 @@
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>861</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>862</v>
-      </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29" t="s">
-        <v>863</v>
-      </c>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
+        <v>980</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>981</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="30" t="s">
+        <v>982</v>
+      </c>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="30"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="30"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="30"/>
+      <c r="X9" s="30"/>
       <c r="Y9" s="12" t="str">
         <f aca="false">IF(LEFT(C9,FIND(":",C9)-1)="off duty","off",LEFT(C9,FIND(":",C9)-1))</f>
         <v>guard</v>
@@ -4948,34 +8398,34 @@
         <v>3</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>865</v>
-      </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29" t="s">
-        <v>866</v>
-      </c>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
+        <v>983</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>984</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="30" t="s">
+        <v>985</v>
+      </c>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="30"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="30"/>
+      <c r="X10" s="30"/>
       <c r="Y10" s="12" t="str">
         <f aca="false">IF(LEFT(C10,FIND(":",C10)-1)="off duty","off",LEFT(C10,FIND(":",C10)-1))</f>
         <v>walk</v>
@@ -4990,34 +8440,34 @@
         <v>4</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>868</v>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29" t="s">
-        <v>869</v>
-      </c>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
+        <v>986</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>987</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="30" t="s">
+        <v>988</v>
+      </c>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
       <c r="Y11" s="12" t="str">
         <f aca="false">IF(LEFT(C11,FIND(":",C11)-1)="off duty","off",LEFT(C11,FIND(":",C11)-1))</f>
         <v>work</v>
@@ -5032,34 +8482,34 @@
         <v>5</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>870</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>871</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29" t="s">
-        <v>872</v>
-      </c>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29"/>
+        <v>989</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>990</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30" t="s">
+        <v>991</v>
+      </c>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
       <c r="Y12" s="12" t="str">
         <f aca="false">IF(LEFT(C12,FIND(":",C12)-1)="off duty","off",LEFT(C12,FIND(":",C12)-1))</f>
         <v>work</v>
@@ -5074,34 +8524,34 @@
         <v>6</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>873</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>874</v>
-      </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29" t="s">
-        <v>875</v>
-      </c>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
+        <v>992</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>993</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30" t="s">
+        <v>994</v>
+      </c>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="30"/>
       <c r="Y13" s="12" t="str">
         <f aca="false">IF(LEFT(C13,FIND(":",C13)-1)="off duty","off",LEFT(C13,FIND(":",C13)-1))</f>
         <v>work</v>
@@ -5116,34 +8566,34 @@
         <v>7</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>876</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>877</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29" t="s">
-        <v>878</v>
-      </c>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
+        <v>995</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>996</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="30"/>
       <c r="Y14" s="12" t="str">
         <f aca="false">IF(LEFT(C14,FIND(":",C14)-1)="off duty","off",LEFT(C14,FIND(":",C14)-1))</f>
         <v>walk</v>
@@ -5158,34 +8608,34 @@
         <v>8</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>879</v>
-      </c>
-      <c r="C15" s="29" t="s">
-        <v>880</v>
-      </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29"/>
-      <c r="M15" s="29"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="29" t="s">
-        <v>881</v>
-      </c>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
+        <v>998</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>999</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="30" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="30"/>
+      <c r="X15" s="30"/>
       <c r="Y15" s="12" t="str">
         <f aca="false">IF(LEFT(C15,FIND(":",C15)-1)="off duty","off",LEFT(C15,FIND(":",C15)-1))</f>
         <v>run</v>
@@ -5197,86 +8647,86 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>882</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>852</v>
+        <v>971</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="C18" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="30" t="n">
+        <v>972</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="30" t="n">
+      <c r="G18" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="30" t="n">
+      <c r="H18" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="30" t="n">
+      <c r="I18" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="J18" s="30" t="n">
+      <c r="J18" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="K18" s="30" t="n">
+      <c r="K18" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="L18" s="30" t="n">
+      <c r="L18" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="M18" s="30" t="n">
+      <c r="M18" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="N18" s="30" t="n">
+      <c r="N18" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="O18" s="30" t="n">
+      <c r="O18" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="P18" s="30" t="n">
+      <c r="P18" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="Q18" s="30" t="n">
+      <c r="Q18" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="R18" s="30" t="n">
+      <c r="R18" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="S18" s="30" t="n">
+      <c r="S18" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="T18" s="30" t="n">
+      <c r="T18" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="U18" s="30" t="n">
+      <c r="U18" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="V18" s="30" t="n">
+      <c r="V18" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="W18" s="30" t="n">
+      <c r="W18" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="X18" s="30" t="n">
+      <c r="X18" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="Y18" s="30" t="n">
+      <c r="Y18" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="Z18" s="30" t="n">
+      <c r="Z18" s="31" t="n">
         <v>23</v>
       </c>
     </row>
@@ -5288,99 +8738,99 @@
         <f aca="false">B8</f>
         <v>SENTRY</v>
       </c>
-      <c r="C19" s="31" t="str">
+      <c r="C19" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="D19" s="31" t="str">
+      <c r="D19" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="E19" s="31" t="str">
+      <c r="E19" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="F19" s="31" t="str">
+      <c r="F19" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="G19" s="31" t="str">
+      <c r="G19" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="H19" s="31" t="str">
+      <c r="H19" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="I19" s="31" t="str">
+      <c r="I19" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="J19" s="31" t="str">
+      <c r="J19" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="K19" s="31" t="str">
+      <c r="K19" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="L19" s="31" t="str">
+      <c r="L19" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="M19" s="31" t="str">
+      <c r="M19" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="N19" s="31" t="str">
+      <c r="N19" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="O19" s="31" t="str">
+      <c r="O19" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="P19" s="31" t="str">
+      <c r="P19" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="Q19" s="31" t="str">
+      <c r="Q19" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="R19" s="31" t="str">
+      <c r="R19" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="S19" s="31" t="str">
+      <c r="S19" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="T19" s="31" t="str">
+      <c r="T19" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="U19" s="31" t="str">
+      <c r="U19" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="V19" s="31" t="str">
+      <c r="V19" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="W19" s="31" t="str">
+      <c r="W19" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="X19" s="31" t="str">
+      <c r="X19" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="Y19" s="31" t="str">
+      <c r="Y19" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
-      <c r="Z19" s="31" t="str">
+      <c r="Z19" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$8,$Z$8)</f>
         <v>guard</v>
       </c>
@@ -5393,99 +8843,99 @@
         <f aca="false">B9</f>
         <v>WATCH</v>
       </c>
-      <c r="C20" s="31" t="str">
+      <c r="C20" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="D20" s="31" t="str">
+      <c r="D20" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="E20" s="31" t="str">
+      <c r="E20" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="F20" s="31" t="str">
+      <c r="F20" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="G20" s="31" t="str">
+      <c r="G20" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="H20" s="31" t="str">
+      <c r="H20" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="I20" s="31" t="str">
+      <c r="I20" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="J20" s="31" t="str">
+      <c r="J20" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="K20" s="31" t="str">
+      <c r="K20" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="L20" s="31" t="str">
+      <c r="L20" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="M20" s="31" t="str">
+      <c r="M20" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="N20" s="31" t="str">
+      <c r="N20" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="O20" s="31" t="str">
+      <c r="O20" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="P20" s="31" t="str">
+      <c r="P20" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="Q20" s="31" t="str">
+      <c r="Q20" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="R20" s="31" t="str">
+      <c r="R20" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="S20" s="31" t="str">
+      <c r="S20" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="T20" s="31" t="str">
+      <c r="T20" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="U20" s="31" t="str">
+      <c r="U20" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="V20" s="31" t="str">
+      <c r="V20" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="W20" s="31" t="str">
+      <c r="W20" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="X20" s="31" t="str">
+      <c r="X20" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="Y20" s="31" t="str">
+      <c r="Y20" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
-      <c r="Z20" s="31" t="str">
+      <c r="Z20" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$9,$Z$9)</f>
         <v>guard</v>
       </c>
@@ -5498,99 +8948,99 @@
         <f aca="false">B10</f>
         <v>GUNNER</v>
       </c>
-      <c r="C21" s="31" t="str">
+      <c r="C21" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="D21" s="31" t="str">
+      <c r="D21" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="E21" s="31" t="str">
+      <c r="E21" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="F21" s="31" t="str">
+      <c r="F21" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="G21" s="31" t="str">
+      <c r="G21" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="H21" s="31" t="str">
+      <c r="H21" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="I21" s="31" t="str">
+      <c r="I21" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="J21" s="31" t="str">
+      <c r="J21" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="K21" s="31" t="str">
+      <c r="K21" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="L21" s="31" t="str">
+      <c r="L21" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="M21" s="31" t="str">
+      <c r="M21" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="N21" s="31" t="str">
+      <c r="N21" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="O21" s="31" t="str">
+      <c r="O21" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="P21" s="31" t="str">
+      <c r="P21" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="Q21" s="31" t="str">
+      <c r="Q21" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="R21" s="31" t="str">
+      <c r="R21" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="S21" s="31" t="str">
+      <c r="S21" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="T21" s="31" t="str">
+      <c r="T21" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>walk</v>
       </c>
-      <c r="U21" s="31" t="str">
+      <c r="U21" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="V21" s="31" t="str">
+      <c r="V21" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="W21" s="31" t="str">
+      <c r="W21" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="X21" s="31" t="str">
+      <c r="X21" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="Y21" s="31" t="str">
+      <c r="Y21" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
-      <c r="Z21" s="31" t="str">
+      <c r="Z21" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$10,$Z$10)</f>
         <v>guard</v>
       </c>
@@ -5603,99 +9053,99 @@
         <f aca="false">B11</f>
         <v>MECHANIC</v>
       </c>
-      <c r="C22" s="31" t="str">
+      <c r="C22" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="D22" s="31" t="str">
+      <c r="D22" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="E22" s="31" t="str">
+      <c r="E22" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="F22" s="31" t="str">
+      <c r="F22" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="G22" s="31" t="str">
+      <c r="G22" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="H22" s="31" t="str">
+      <c r="H22" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="I22" s="31" t="str">
+      <c r="I22" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="J22" s="31" t="str">
+      <c r="J22" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="K22" s="31" t="str">
+      <c r="K22" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="L22" s="31" t="str">
+      <c r="L22" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="M22" s="31" t="str">
+      <c r="M22" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="N22" s="31" t="str">
+      <c r="N22" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="O22" s="31" t="str">
+      <c r="O22" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="P22" s="31" t="str">
+      <c r="P22" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="Q22" s="31" t="str">
+      <c r="Q22" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="R22" s="31" t="str">
+      <c r="R22" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="S22" s="31" t="str">
+      <c r="S22" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="T22" s="31" t="str">
+      <c r="T22" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>work</v>
       </c>
-      <c r="U22" s="31" t="str">
+      <c r="U22" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="V22" s="31" t="str">
+      <c r="V22" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="W22" s="31" t="str">
+      <c r="W22" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="X22" s="31" t="str">
+      <c r="X22" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="Y22" s="31" t="str">
+      <c r="Y22" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
-      <c r="Z22" s="31" t="str">
+      <c r="Z22" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$11,$Z$11)</f>
         <v>off</v>
       </c>
@@ -5708,99 +9158,99 @@
         <f aca="false">B12</f>
         <v>LOGISTICS</v>
       </c>
-      <c r="C23" s="31" t="str">
+      <c r="C23" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="D23" s="31" t="str">
+      <c r="D23" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="E23" s="31" t="str">
+      <c r="E23" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="F23" s="31" t="str">
+      <c r="F23" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="G23" s="31" t="str">
+      <c r="G23" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="H23" s="31" t="str">
+      <c r="H23" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="I23" s="31" t="str">
+      <c r="I23" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="J23" s="31" t="str">
+      <c r="J23" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="K23" s="31" t="str">
+      <c r="K23" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="L23" s="31" t="str">
+      <c r="L23" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="M23" s="31" t="str">
+      <c r="M23" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="N23" s="31" t="str">
+      <c r="N23" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="O23" s="31" t="str">
+      <c r="O23" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="P23" s="31" t="str">
+      <c r="P23" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="Q23" s="31" t="str">
+      <c r="Q23" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="R23" s="31" t="str">
+      <c r="R23" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="S23" s="31" t="str">
+      <c r="S23" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="T23" s="31" t="str">
+      <c r="T23" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>work</v>
       </c>
-      <c r="U23" s="31" t="str">
+      <c r="U23" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="V23" s="31" t="str">
+      <c r="V23" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="W23" s="31" t="str">
+      <c r="W23" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="X23" s="31" t="str">
+      <c r="X23" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="Y23" s="31" t="str">
+      <c r="Y23" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
-      <c r="Z23" s="31" t="str">
+      <c r="Z23" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$12,$Z$12)</f>
         <v>off</v>
       </c>
@@ -5813,99 +9263,99 @@
         <f aca="false">B13</f>
         <v>TECHNICIAN</v>
       </c>
-      <c r="C24" s="31" t="str">
+      <c r="C24" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="D24" s="31" t="str">
+      <c r="D24" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="E24" s="31" t="str">
+      <c r="E24" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="F24" s="31" t="str">
+      <c r="F24" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="G24" s="31" t="str">
+      <c r="G24" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="H24" s="31" t="str">
+      <c r="H24" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="I24" s="31" t="str">
+      <c r="I24" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="J24" s="31" t="str">
+      <c r="J24" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="K24" s="31" t="str">
+      <c r="K24" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="L24" s="31" t="str">
+      <c r="L24" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="M24" s="31" t="str">
+      <c r="M24" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="N24" s="31" t="str">
+      <c r="N24" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="O24" s="31" t="str">
+      <c r="O24" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="P24" s="31" t="str">
+      <c r="P24" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="Q24" s="31" t="str">
+      <c r="Q24" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="R24" s="31" t="str">
+      <c r="R24" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="S24" s="31" t="str">
+      <c r="S24" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="T24" s="31" t="str">
+      <c r="T24" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="U24" s="31" t="str">
+      <c r="U24" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="V24" s="31" t="str">
+      <c r="V24" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="W24" s="31" t="str">
+      <c r="W24" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="X24" s="31" t="str">
+      <c r="X24" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="Y24" s="31" t="str">
+      <c r="Y24" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
-      <c r="Z24" s="31" t="str">
+      <c r="Z24" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$13,$Z$13)</f>
         <v>work</v>
       </c>
@@ -5918,99 +9368,99 @@
         <f aca="false">B14</f>
         <v>PATROL</v>
       </c>
-      <c r="C25" s="31" t="str">
+      <c r="C25" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="D25" s="31" t="str">
+      <c r="D25" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="E25" s="31" t="str">
+      <c r="E25" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="F25" s="31" t="str">
+      <c r="F25" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="G25" s="31" t="str">
+      <c r="G25" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="H25" s="31" t="str">
+      <c r="H25" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="I25" s="31" t="str">
+      <c r="I25" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="J25" s="31" t="str">
+      <c r="J25" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="K25" s="31" t="str">
+      <c r="K25" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="L25" s="31" t="str">
+      <c r="L25" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="M25" s="31" t="str">
+      <c r="M25" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="N25" s="31" t="str">
+      <c r="N25" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="O25" s="31" t="str">
+      <c r="O25" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="P25" s="31" t="str">
+      <c r="P25" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="Q25" s="31" t="str">
+      <c r="Q25" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="R25" s="31" t="str">
+      <c r="R25" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="S25" s="31" t="str">
+      <c r="S25" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="T25" s="31" t="str">
+      <c r="T25" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>walk</v>
       </c>
-      <c r="U25" s="31" t="str">
+      <c r="U25" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="V25" s="31" t="str">
+      <c r="V25" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="W25" s="31" t="str">
+      <c r="W25" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="X25" s="31" t="str">
+      <c r="X25" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="Y25" s="31" t="str">
+      <c r="Y25" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
-      <c r="Z25" s="31" t="str">
+      <c r="Z25" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$14,$Z$14)</f>
         <v>guard</v>
       </c>
@@ -6023,106 +9473,106 @@
         <f aca="false">B15</f>
         <v>RUNNER</v>
       </c>
-      <c r="C26" s="31" t="str">
+      <c r="C26" s="32" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="D26" s="31" t="str">
+      <c r="D26" s="32" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="E26" s="31" t="str">
+      <c r="E26" s="32" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="F26" s="31" t="str">
+      <c r="F26" s="32" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="G26" s="31" t="str">
+      <c r="G26" s="32" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="H26" s="31" t="str">
+      <c r="H26" s="32" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="I26" s="31" t="str">
+      <c r="I26" s="32" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="J26" s="31" t="str">
+      <c r="J26" s="32" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="K26" s="31" t="str">
+      <c r="K26" s="32" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="L26" s="31" t="str">
+      <c r="L26" s="32" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="M26" s="31" t="str">
+      <c r="M26" s="32" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="N26" s="31" t="str">
+      <c r="N26" s="32" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="O26" s="31" t="str">
+      <c r="O26" s="32" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="P26" s="31" t="str">
+      <c r="P26" s="32" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="Q26" s="31" t="str">
+      <c r="Q26" s="32" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="R26" s="31" t="str">
+      <c r="R26" s="32" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="S26" s="31" t="str">
+      <c r="S26" s="32" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="T26" s="31" t="str">
+      <c r="T26" s="32" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>run</v>
       </c>
-      <c r="U26" s="31" t="str">
+      <c r="U26" s="32" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="V26" s="31" t="str">
+      <c r="V26" s="32" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="W26" s="31" t="str">
+      <c r="W26" s="32" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="X26" s="31" t="str">
+      <c r="X26" s="32" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="Y26" s="31" t="str">
+      <c r="Y26" s="32" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
-      <c r="Z26" s="31" t="str">
+      <c r="Z26" s="32" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),$Y$15,$Z$15)</f>
         <v>off</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>883</v>
+        <v>1002</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="14" t="n">
@@ -6224,119 +9674,119 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>884</v>
+        <v>1003</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="32" t="str">
+      <c r="C28" s="33" t="str">
         <f aca="false">IF(AND(C$18+0.5&gt;=$D$5,C$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="D28" s="32" t="str">
+      <c r="D28" s="33" t="str">
         <f aca="false">IF(AND(D$18+0.5&gt;=$D$5,D$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="E28" s="32" t="str">
+      <c r="E28" s="33" t="str">
         <f aca="false">IF(AND(E$18+0.5&gt;=$D$5,E$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="F28" s="32" t="str">
+      <c r="F28" s="33" t="str">
         <f aca="false">IF(AND(F$18+0.5&gt;=$D$5,F$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="G28" s="32" t="str">
+      <c r="G28" s="33" t="str">
         <f aca="false">IF(AND(G$18+0.5&gt;=$D$5,G$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="H28" s="32" t="str">
+      <c r="H28" s="33" t="str">
         <f aca="false">IF(AND(H$18+0.5&gt;=$D$5,H$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="I28" s="32" t="str">
+      <c r="I28" s="33" t="str">
         <f aca="false">IF(AND(I$18+0.5&gt;=$D$5,I$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="J28" s="32" t="str">
+      <c r="J28" s="33" t="str">
         <f aca="false">IF(AND(J$18+0.5&gt;=$D$5,J$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="K28" s="32" t="str">
+      <c r="K28" s="33" t="str">
         <f aca="false">IF(AND(K$18+0.5&gt;=$D$5,K$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="L28" s="32" t="str">
+      <c r="L28" s="33" t="str">
         <f aca="false">IF(AND(L$18+0.5&gt;=$D$5,L$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="M28" s="32" t="str">
+      <c r="M28" s="33" t="str">
         <f aca="false">IF(AND(M$18+0.5&gt;=$D$5,M$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="N28" s="32" t="str">
+      <c r="N28" s="33" t="str">
         <f aca="false">IF(AND(N$18+0.5&gt;=$D$5,N$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="O28" s="32" t="str">
+      <c r="O28" s="33" t="str">
         <f aca="false">IF(AND(O$18+0.5&gt;=$D$5,O$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="P28" s="32" t="str">
+      <c r="P28" s="33" t="str">
         <f aca="false">IF(AND(P$18+0.5&gt;=$D$5,P$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="Q28" s="32" t="str">
+      <c r="Q28" s="33" t="str">
         <f aca="false">IF(AND(Q$18+0.5&gt;=$D$5,Q$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="R28" s="32" t="str">
+      <c r="R28" s="33" t="str">
         <f aca="false">IF(AND(R$18+0.5&gt;=$D$5,R$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="S28" s="32" t="str">
+      <c r="S28" s="33" t="str">
         <f aca="false">IF(AND(S$18+0.5&gt;=$D$5,S$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="T28" s="32" t="str">
+      <c r="T28" s="33" t="str">
         <f aca="false">IF(AND(T$18+0.5&gt;=$D$5,T$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>DAY</v>
       </c>
-      <c r="U28" s="32" t="str">
+      <c r="U28" s="33" t="str">
         <f aca="false">IF(AND(U$18+0.5&gt;=$D$5,U$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="V28" s="32" t="str">
+      <c r="V28" s="33" t="str">
         <f aca="false">IF(AND(V$18+0.5&gt;=$D$5,V$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="W28" s="32" t="str">
+      <c r="W28" s="33" t="str">
         <f aca="false">IF(AND(W$18+0.5&gt;=$D$5,W$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="X28" s="32" t="str">
+      <c r="X28" s="33" t="str">
         <f aca="false">IF(AND(X$18+0.5&gt;=$D$5,X$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="Y28" s="32" t="str">
+      <c r="Y28" s="33" t="str">
         <f aca="false">IF(AND(Y$18+0.5&gt;=$D$5,Y$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
-      <c r="Z28" s="32" t="str">
+      <c r="Z28" s="33" t="str">
         <f aca="false">IF(AND(Z$18+0.5&gt;=$D$5,Z$18+0.5&lt;$H$5),"DAY","NIGHT")</f>
         <v>NIGHT</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>885</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>886</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>887</v>
+        <v>1006</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="9" t="n">
@@ -6374,53 +9824,53 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>888</v>
+        <v>1007</v>
       </c>
       <c r="B33" s="4"/>
-      <c r="C33" s="33" t="n">
+      <c r="C33" s="34" t="n">
         <f aca="false">1+2.5*C32</f>
         <v>1</v>
       </c>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33" t="n">
+      <c r="D33" s="34"/>
+      <c r="E33" s="34" t="n">
         <f aca="false">1+2.5*E32</f>
         <v>3.5</v>
       </c>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33" t="n">
+      <c r="F33" s="34"/>
+      <c r="G33" s="34" t="n">
         <f aca="false">1+2.5*G32</f>
         <v>6</v>
       </c>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33" t="n">
+      <c r="H33" s="34"/>
+      <c r="I33" s="34" t="n">
         <f aca="false">1+2.5*I32</f>
         <v>8.5</v>
       </c>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33" t="n">
+      <c r="J33" s="34"/>
+      <c r="K33" s="34" t="n">
         <f aca="false">1+2.5*K32</f>
         <v>11</v>
       </c>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33" t="n">
+      <c r="L33" s="34"/>
+      <c r="M33" s="34" t="n">
         <f aca="false">1+2.5*M32</f>
         <v>13.5</v>
       </c>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33" t="n">
+      <c r="N33" s="34"/>
+      <c r="O33" s="34" t="n">
         <f aca="false">1+2.5*O32</f>
         <v>16</v>
       </c>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33" t="n">
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34" t="n">
         <f aca="false">1+2.5*Q32</f>
         <v>18.5</v>
       </c>
-      <c r="R33" s="33"/>
+      <c r="R33" s="34"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>889</v>
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
@@ -6506,7 +9956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -6523,7 +9973,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>890</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6533,46 +9983,46 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>891</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>892</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>893</v>
+        <v>1012</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>894</v>
+        <v>1013</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>895</v>
+        <v>1014</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>896</v>
+        <v>1015</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>897</v>
+        <v>1016</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>898</v>
+        <v>1017</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>899</v>
+        <v>1018</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>900</v>
+        <v>1019</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>901</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>902</v>
+        <v>1021</v>
       </c>
       <c r="B7" s="21" t="n">
         <v>14.8698</v>
@@ -6604,7 +10054,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>903</v>
+        <v>1022</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>16.3802</v>
@@ -6636,7 +10086,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>904</v>
+        <v>1023</v>
       </c>
       <c r="B9" s="21" t="n">
         <v>10.717</v>
@@ -6668,7 +10118,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>905</v>
+        <v>1024</v>
       </c>
       <c r="B10" s="21" t="n">
         <v>12.6203</v>
@@ -6700,7 +10150,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>906</v>
+        <v>1025</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>16.4236</v>
@@ -6732,7 +10182,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>907</v>
+        <v>1026</v>
       </c>
       <c r="B12" s="21" t="n">
         <v>17.1765</v>
@@ -6764,7 +10214,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>908</v>
+        <v>1027</v>
       </c>
       <c r="B13" s="21" t="n">
         <v>54.4709</v>
@@ -6796,7 +10246,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>909</v>
+        <v>1028</v>
       </c>
       <c r="B14" s="21" t="n">
         <v>16.7587</v>
@@ -6828,7 +10278,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>910</v>
+        <v>1029</v>
       </c>
       <c r="B15" s="21" t="n">
         <v>15.1059</v>
@@ -6860,7 +10310,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>911</v>
+        <v>1030</v>
       </c>
       <c r="B16" s="21" t="n">
         <v>14.1625</v>
@@ -6892,7 +10342,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>912</v>
+        <v>1031</v>
       </c>
       <c r="B17" s="21" t="n">
         <v>13.009</v>

--- a/report/workbooks/cg_workbook_values.xlsx
+++ b/report/workbooks/cg_workbook_values.xlsx
@@ -2389,7 +2389,7 @@
     <t xml:space="preserve">Illumination: ambient + Lambert diffuse + Blinn-Phong specular at one roof point</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: scene/DayCycle (solar model, transmittance, 3.2 smoothstep(-1, 10, e), ambient mixLog); export 'lights'; ShaderSources.cpp brdf(); BNK-171 'Roof slab A'.</t>
+    <t xml:space="preserve">Source: scene/DayCycle (solar model, transmittance, 3.2 smoothstep(-1, 10, e), ambient mixLog); export 'lights'; ShaderSources.cpp brdf(); the command bunker's part 'Roof slab A'.</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity</t>
@@ -2503,7 +2503,7 @@
     <t xml:space="preserve">L.y (unit)</t>
   </si>
   <si>
-    <t xml:space="preserve">roof albedo kd (BNK-171 colour)</t>
+    <t xml:space="preserve">roof albedo kd (Roof slab A colour)</t>
   </si>
   <si>
     <t xml:space="preserve">L.z (unit)</t>
@@ -4626,11 +4626,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="28108801"/>
-        <c:axId val="70504713"/>
+        <c:axId val="54820344"/>
+        <c:axId val="37425226"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="28108801"/>
+        <c:axId val="54820344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4663,7 +4663,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70504713"/>
+        <c:crossAx val="37425226"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4671,7 +4671,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70504713"/>
+        <c:axId val="37425226"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4747,7 +4747,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28108801"/>
+        <c:crossAx val="54820344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5218,11 +5218,11 @@
         <v>0</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>2443</v>
+        <v>2452</v>
       </c>
       <c r="Q7" s="7" t="n">
         <f aca="false">M7*P7</f>
-        <v>29316</v>
+        <v>29424</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5279,11 +5279,11 @@
         <v>0</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="Q8" s="7" t="n">
         <f aca="false">M8*P8</f>
-        <v>988992</v>
+        <v>991440</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5401,11 +5401,11 @@
         <v>0</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="Q10" s="7" t="n">
         <f aca="false">M10*P10</f>
-        <v>195552</v>
+        <v>195840</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6085,11 +6085,11 @@
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">SUM(P6:P21)</f>
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="Q22" s="7" t="n">
         <f aca="false">SUM(Q6:Q21)</f>
-        <v>1597236</v>
+        <v>1600080</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13994,7 +13994,7 @@
         <v>144</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C10" s="8" t="n">
         <v>1</v>
@@ -14002,7 +14002,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>1</v>
@@ -14011,7 +14011,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -14021,10 +14021,10 @@
       <c r="O10" s="7"/>
       <c r="P10" s="7" t="n">
         <f aca="false">SUM(B10:O10)</f>
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="R10" s="12" t="str">
         <f aca="false">IF(P10=Q10,"OK","DIFF")</f>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">SUM(B7:B37)</f>
-        <v>2467</v>
+        <v>2476</v>
       </c>
       <c r="C38" s="7" t="n">
         <f aca="false">SUM(C7:C37)</f>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="F38" s="7" t="n">
         <f aca="false">SUM(F7:F37)</f>
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G38" s="7" t="n">
         <f aca="false">SUM(G7:G37)</f>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="I38" s="7" t="n">
         <f aca="false">SUM(I7:I37)</f>
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="J38" s="7" t="n">
         <f aca="false">SUM(J7:J37)</f>
@@ -15598,11 +15598,11 @@
       </c>
       <c r="P38" s="7" t="n">
         <f aca="false">SUM(P7:P37)</f>
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="Q38" s="7" t="n">
         <f aca="false">SUM(Q7:Q37)</f>
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="S38" s="7" t="n">
         <f aca="false">SUM(S7:S37)</f>
@@ -15618,7 +15618,7 @@
         <v>176</v>
       </c>
       <c r="B39" s="8" t="n">
-        <v>2467</v>
+        <v>2476</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>6</v>
@@ -15630,7 +15630,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>10</v>
@@ -15639,7 +15639,7 @@
         <v>364</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>3</v>
@@ -15661,10 +15661,10 @@
       </c>
       <c r="P39" s="7" t="n">
         <f aca="false">SUM(B39:O39)</f>
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>5476</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25293,18 +25293,18 @@
         <v>1</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="F20" s="7" t="n">
         <f aca="false">IF(ISNUMBER(D20),C20*D20,E20)</f>
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="8" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>1</v>
@@ -25312,7 +25312,7 @@
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M20" s="8" t="n">
         <v>1</v>
@@ -25321,7 +25321,7 @@
         <v>9</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
@@ -25331,7 +25331,7 @@
       <c r="U20" s="7"/>
       <c r="V20" s="7" t="n">
         <f aca="false">SUM(G20:U20)</f>
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="W20" s="12" t="str">
         <f aca="false">IF(AND(V20=E20,F20=E20),"OK","DIFF")</f>
@@ -27674,11 +27674,11 @@
       </c>
       <c r="E69" s="7" t="n">
         <f aca="false">SUM(E7:E68)</f>
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="F69" s="7" t="n">
         <f aca="false">SUM(F7:F68)</f>
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="G69" s="7" t="n">
         <f aca="false">SUM(G7:G68)</f>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="H69" s="7" t="n">
         <f aca="false">SUM(H7:H68)</f>
-        <v>2443</v>
+        <v>2452</v>
       </c>
       <c r="I69" s="7" t="n">
         <f aca="false">SUM(I7:I68)</f>
@@ -27702,7 +27702,7 @@
       </c>
       <c r="L69" s="7" t="n">
         <f aca="false">SUM(L7:L68)</f>
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="M69" s="7" t="n">
         <f aca="false">SUM(M7:M68)</f>
@@ -27714,7 +27714,7 @@
       </c>
       <c r="O69" s="7" t="n">
         <f aca="false">SUM(O7:O68)</f>
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="P69" s="7" t="n">
         <f aca="false">SUM(P7:P68)</f>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="V69" s="7" t="n">
         <f aca="false">SUM(V7:V68)</f>
-        <v>5476</v>
+        <v>5489</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27750,7 +27750,7 @@
         <v>547</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>5476</v>
+        <v>5489</v>
       </c>
       <c r="F70" s="12" t="str">
         <f aca="false">IF(E69=E70,"OK","DIFF")</f>

--- a/report/workbooks/cg_workbook_values.xlsx
+++ b/report/workbooks/cg_workbook_values.xlsx
@@ -1591,7 +1591,7 @@
     <t xml:space="preserve">Earth revetment</t>
   </si>
   <si>
-    <t xml:space="preserve">48..60</t>
+    <t xml:space="preserve">42..56</t>
   </si>
   <si>
     <t xml:space="preserve">Radar surround</t>
@@ -4626,11 +4626,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="54820344"/>
-        <c:axId val="37425226"/>
+        <c:axId val="37479949"/>
+        <c:axId val="32096833"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="54820344"/>
+        <c:axId val="37479949"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4663,7 +4663,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37425226"/>
+        <c:crossAx val="32096833"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4671,7 +4671,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="37425226"/>
+        <c:axId val="32096833"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4747,7 +4747,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54820344"/>
+        <c:crossAx val="37479949"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5218,11 +5218,11 @@
         <v>0</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="Q7" s="7" t="n">
         <f aca="false">M7*P7</f>
-        <v>29424</v>
+        <v>29436</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5401,11 +5401,11 @@
         <v>0</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="Q10" s="7" t="n">
         <f aca="false">M10*P10</f>
-        <v>195840</v>
+        <v>195696</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5828,11 +5828,11 @@
         <v>0</v>
       </c>
       <c r="P17" s="8" t="n">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="Q17" s="7" t="n">
         <f aca="false">M17*P17</f>
-        <v>69888</v>
+        <v>67008</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6085,11 +6085,11 @@
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">SUM(P6:P21)</f>
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="Q22" s="7" t="n">
         <f aca="false">SUM(Q6:Q21)</f>
-        <v>1600080</v>
+        <v>1597068</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13855,7 +13855,9 @@
       <c r="A8" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B8" s="7"/>
+      <c r="B8" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
@@ -13865,7 +13867,7 @@
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
       <c r="I8" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="7"/>
       <c r="K8" s="8" t="n">
@@ -13877,10 +13879,10 @@
       <c r="O8" s="7"/>
       <c r="P8" s="7" t="n">
         <f aca="false">SUM(B8:O8)</f>
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R8" s="12" t="str">
         <f aca="false">IF(P8=Q8,"OK","DIFF")</f>
@@ -14965,7 +14967,7 @@
         <v>162</v>
       </c>
       <c r="B25" s="8" t="n">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
@@ -14975,7 +14977,7 @@
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="8" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="I25" s="8" t="n">
         <v>90</v>
@@ -14990,10 +14992,10 @@
       <c r="O25" s="7"/>
       <c r="P25" s="7" t="n">
         <f aca="false">SUM(B25:O25)</f>
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="R25" s="12" t="str">
         <f aca="false">IF(P25=Q25,"OK","DIFF")</f>
@@ -15542,7 +15544,7 @@
       </c>
       <c r="B38" s="7" t="n">
         <f aca="false">SUM(B7:B37)</f>
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="C38" s="7" t="n">
         <f aca="false">SUM(C7:C37)</f>
@@ -15566,11 +15568,11 @@
       </c>
       <c r="H38" s="7" t="n">
         <f aca="false">SUM(H7:H37)</f>
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="I38" s="7" t="n">
         <f aca="false">SUM(I7:I37)</f>
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J38" s="7" t="n">
         <f aca="false">SUM(J7:J37)</f>
@@ -15598,11 +15600,11 @@
       </c>
       <c r="P38" s="7" t="n">
         <f aca="false">SUM(P7:P37)</f>
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="Q38" s="7" t="n">
         <f aca="false">SUM(Q7:Q37)</f>
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="S38" s="7" t="n">
         <f aca="false">SUM(S7:S37)</f>
@@ -15618,7 +15620,7 @@
         <v>176</v>
       </c>
       <c r="B39" s="8" t="n">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="C39" s="8" t="n">
         <v>6</v>
@@ -15636,10 +15638,10 @@
         <v>10</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="I39" s="8" t="n">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="J39" s="8" t="n">
         <v>3</v>
@@ -15661,10 +15663,10 @@
       </c>
       <c r="P39" s="7" t="n">
         <f aca="false">SUM(B39:O39)</f>
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>5489</v>
+        <v>5474</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26304,15 +26306,15 @@
         <v>512</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F40" s="7" t="n">
         <f aca="false">IF(ISNUMBER(D40),C40*D40,E40)</f>
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="8" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
@@ -26320,7 +26322,7 @@
       <c r="L40" s="7"/>
       <c r="M40" s="7"/>
       <c r="N40" s="8" t="n">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="O40" s="7"/>
       <c r="P40" s="7"/>
@@ -26331,7 +26333,7 @@
       <c r="U40" s="7"/>
       <c r="V40" s="7" t="n">
         <f aca="false">SUM(G40:U40)</f>
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="W40" s="12" t="str">
         <f aca="false">IF(AND(V40=E40,F40=E40),"OK","DIFF")</f>
@@ -27394,29 +27396,29 @@
         <v>539</v>
       </c>
       <c r="C63" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D63" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63" s="7" t="n">
         <f aca="false">IF(ISNUMBER(D63),C63*D63,E63)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63" s="7"/>
-      <c r="H63" s="7"/>
+      <c r="H63" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="I63" s="7"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
       <c r="M63" s="7"/>
       <c r="N63" s="7"/>
-      <c r="O63" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="O63" s="7"/>
       <c r="P63" s="7"/>
       <c r="Q63" s="7"/>
       <c r="R63" s="7"/>
@@ -27425,7 +27427,7 @@
       <c r="U63" s="7"/>
       <c r="V63" s="7" t="n">
         <f aca="false">SUM(G63:U63)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W63" s="12" t="str">
         <f aca="false">IF(AND(V63=E63,F63=E63),"OK","DIFF")</f>
@@ -27670,15 +27672,15 @@
       </c>
       <c r="C69" s="7" t="n">
         <f aca="false">SUM(C7:C68)</f>
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E69" s="7" t="n">
         <f aca="false">SUM(E7:E68)</f>
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="F69" s="7" t="n">
         <f aca="false">SUM(F7:F68)</f>
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="G69" s="7" t="n">
         <f aca="false">SUM(G7:G68)</f>
@@ -27686,7 +27688,7 @@
       </c>
       <c r="H69" s="7" t="n">
         <f aca="false">SUM(H7:H68)</f>
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="I69" s="7" t="n">
         <f aca="false">SUM(I7:I68)</f>
@@ -27710,11 +27712,11 @@
       </c>
       <c r="N69" s="7" t="n">
         <f aca="false">SUM(N7:N68)</f>
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="O69" s="7" t="n">
         <f aca="false">SUM(O7:O68)</f>
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="P69" s="7" t="n">
         <f aca="false">SUM(P7:P68)</f>
@@ -27742,7 +27744,7 @@
       </c>
       <c r="V69" s="7" t="n">
         <f aca="false">SUM(V7:V68)</f>
-        <v>5489</v>
+        <v>5474</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27750,7 +27752,7 @@
         <v>547</v>
       </c>
       <c r="E70" s="8" t="n">
-        <v>5489</v>
+        <v>5474</v>
       </c>
       <c r="F70" s="12" t="str">
         <f aca="false">IF(E69=E70,"OK","DIFF")</f>
